--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0002T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0002T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.54981901571102</v>
+        <v>3.339345590053041</v>
       </c>
       <c r="D2" t="n">
-        <v>20.78482507921699</v>
+        <v>3.377534075372762</v>
       </c>
       <c r="E2" t="n">
-        <v>16.4718250863447</v>
+        <v>2.676671576531014</v>
       </c>
       <c r="F2" t="n">
-        <v>9.692628656082574</v>
+        <v>1.575052156613418</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.33886313746626</v>
+        <v>6.717565259838267</v>
       </c>
       <c r="D3" t="n">
-        <v>33.91491609184649</v>
+        <v>5.511173864925055</v>
       </c>
       <c r="E3" t="n">
-        <v>16.4718250863447</v>
+        <v>2.676671576531014</v>
       </c>
       <c r="F3" t="n">
-        <v>9.692628656082574</v>
+        <v>1.575052156613418</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>7.548232054864379</v>
+        <v>1.226587708915462</v>
       </c>
       <c r="D4" t="n">
-        <v>6.800735254367722</v>
+        <v>1.105119478834755</v>
       </c>
       <c r="E4" t="n">
-        <v>16.4718250863447</v>
+        <v>2.676671576531014</v>
       </c>
       <c r="F4" t="n">
-        <v>9.692628656082574</v>
+        <v>1.575052156613418</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>49.07562836067995</v>
+        <v>7.974789608610492</v>
       </c>
       <c r="D5" t="n">
-        <v>23.78187532813694</v>
+        <v>3.864554740822252</v>
       </c>
       <c r="E5" t="n">
-        <v>16.4718250863447</v>
+        <v>2.676671576531014</v>
       </c>
       <c r="F5" t="n">
-        <v>9.692628656082574</v>
+        <v>1.575052156613418</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
